--- a/research/traditional_assets/database/data/namibia/namibia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/namibia/namibia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0481</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.01932</v>
+        <v>0.0284</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.000414763967544867</v>
+        <v>0.000771840357156038</v>
       </c>
       <c r="J2">
-        <v>0.0002975013701918576</v>
+        <v>0.0005618752516703573</v>
       </c>
       <c r="K2">
-        <v>159.5</v>
+        <v>89.3</v>
       </c>
       <c r="L2">
-        <v>0.2519349233928289</v>
+        <v>0.247780244173141</v>
       </c>
       <c r="M2">
-        <v>54.71</v>
+        <v>33.08000000000001</v>
       </c>
       <c r="N2">
-        <v>0.04956962942828667</v>
+        <v>0.06311772562488076</v>
       </c>
       <c r="O2">
-        <v>0.3430094043887147</v>
+        <v>0.3704367301231803</v>
       </c>
       <c r="P2">
-        <v>53.6</v>
+        <v>31.48</v>
       </c>
       <c r="Q2">
-        <v>0.04856392135544079</v>
+        <v>0.0600648731158176</v>
       </c>
       <c r="R2">
-        <v>0.3360501567398119</v>
+        <v>0.3525195968645017</v>
       </c>
       <c r="S2">
-        <v>1.109999999999999</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="T2">
-        <v>0.02028879546700785</v>
+        <v>0.04836759371221285</v>
       </c>
       <c r="U2">
-        <v>660.9</v>
+        <v>416.1</v>
       </c>
       <c r="V2">
-        <v>0.5988040228322913</v>
+        <v>0.793932455638237</v>
       </c>
       <c r="W2">
-        <v>0.1679032701291564</v>
+        <v>0.1112936132178734</v>
       </c>
       <c r="X2">
-        <v>0.07815296210599661</v>
+        <v>0.1457492804834416</v>
       </c>
       <c r="Y2">
-        <v>0.08975030802315977</v>
+        <v>-0.0344556672655682</v>
       </c>
       <c r="Z2">
-        <v>0.6342435000198839</v>
+        <v>0.3646503116408398</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.0002868511851250123</v>
       </c>
       <c r="AB2">
-        <v>0.06449469823636031</v>
+        <v>0.1075501914334558</v>
       </c>
       <c r="AC2">
-        <v>-0.06379161336733466</v>
+        <v>-0.1072633402483308</v>
       </c>
       <c r="AD2">
-        <v>769</v>
+        <v>585.3</v>
       </c>
       <c r="AE2">
-        <v>0.4970646607367235</v>
+        <v>0.7241436764048195</v>
       </c>
       <c r="AF2">
-        <v>769.4970646607368</v>
+        <v>586.0241436764048</v>
       </c>
       <c r="AG2">
-        <v>108.5970646607368</v>
+        <v>169.9241436764048</v>
       </c>
       <c r="AH2">
-        <v>0.4107934392904378</v>
+        <v>0.5278906390916471</v>
       </c>
       <c r="AI2">
-        <v>0.3918613917130241</v>
+        <v>0.4373562088884423</v>
       </c>
       <c r="AJ2">
-        <v>0.08957958228755412</v>
+        <v>0.2448389515331235</v>
       </c>
       <c r="AK2">
-        <v>0.08335685396176166</v>
+        <v>0.1839355951449624</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>2124.309392265193</v>
+        <v>1383.687943262411</v>
       </c>
       <c r="AP2">
-        <v>299.9918913280022</v>
+        <v>401.7119235848813</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FirstRand Namibia Limited (NMSE:FNB)</t>
+          <t>SBN Holdings Limited (NMSE:SNO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,12 +715,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0271</v>
-      </c>
-      <c r="E3">
-        <v>-0.0313</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -728,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.00201136127779491</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.001464845684885493</v>
       </c>
       <c r="K3">
-        <v>71.59999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="L3">
-        <v>0.2794691647150663</v>
+        <v>0.1836587129428778</v>
       </c>
       <c r="M3">
-        <v>26.4</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N3">
-        <v>0.05384458494799102</v>
+        <v>0.07291512915129152</v>
       </c>
       <c r="O3">
-        <v>0.3687150837988827</v>
+        <v>0.388976377952756</v>
       </c>
       <c r="P3">
-        <v>26.4</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.05384458494799102</v>
+        <v>0.07291512915129152</v>
       </c>
       <c r="R3">
-        <v>0.3687150837988827</v>
+        <v>0.388976377952756</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,61 +758,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>64.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1319600244748113</v>
+        <v>0.6243542435424354</v>
       </c>
       <c r="W3">
-        <v>0.2513162513162513</v>
+        <v>0.08472314876584389</v>
       </c>
       <c r="X3">
-        <v>0.06606609944681961</v>
+        <v>0.1461012017982734</v>
       </c>
       <c r="Y3">
-        <v>0.1852501518694317</v>
+        <v>-0.06137805303242946</v>
       </c>
       <c r="Z3">
-        <v>0.7519812151452892</v>
+        <v>0.3916469674379871</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.0005737023702500247</v>
       </c>
       <c r="AB3">
-        <v>0.06192378119290903</v>
+        <v>0.1055115993439438</v>
       </c>
       <c r="AC3">
-        <v>-0.06192378119290903</v>
+        <v>-0.1049378969736938</v>
       </c>
       <c r="AD3">
-        <v>101.5</v>
+        <v>152.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.7241436764048195</v>
       </c>
       <c r="AF3">
-        <v>101.5</v>
+        <v>153.2241436764048</v>
       </c>
       <c r="AG3">
-        <v>36.8</v>
+        <v>68.62414367640483</v>
       </c>
       <c r="AH3">
-        <v>0.1715106454883407</v>
+        <v>0.530693906388843</v>
       </c>
       <c r="AI3">
-        <v>0.204184268758801</v>
+        <v>0.3554060841264611</v>
       </c>
       <c r="AJ3">
-        <v>0.06981597419844431</v>
+        <v>0.3361882746471859</v>
       </c>
       <c r="AK3">
-        <v>0.08510638297872339</v>
+        <v>0.1980356778270787</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>360.5200945626478</v>
+      </c>
+      <c r="AP3">
+        <v>162.2320181475291</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SBN Holdings Limited (NMSE:SNO)</t>
+          <t>Capricorn Group Limited (NMSE:CGP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,6 +837,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.0284</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -844,224 +850,96 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.001788740244227897</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.001296957212122114</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>26.8</v>
+        <v>63.9</v>
       </c>
       <c r="L4">
-        <v>0.1825613079019074</v>
+        <v>0.2877082395317425</v>
       </c>
       <c r="M4">
-        <v>12.8</v>
+        <v>23.2</v>
       </c>
       <c r="N4">
-        <v>0.06377678126557051</v>
+        <v>0.05970149253731344</v>
       </c>
       <c r="O4">
-        <v>0.4776119402985075</v>
+        <v>0.3630672926447575</v>
       </c>
       <c r="P4">
-        <v>12.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q4">
-        <v>0.06377678126557051</v>
+        <v>0.05558414822439527</v>
       </c>
       <c r="R4">
-        <v>0.4776119402985075</v>
+        <v>0.3380281690140846</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.06896551724137936</v>
       </c>
       <c r="U4">
-        <v>68.3</v>
+        <v>331.5</v>
       </c>
       <c r="V4">
-        <v>0.3403089187842551</v>
+        <v>0.8530622748327329</v>
       </c>
       <c r="W4">
-        <v>0.1138971525711857</v>
+        <v>0.1378640776699029</v>
       </c>
       <c r="X4">
-        <v>0.07815296210599661</v>
+        <v>0.1453973591686099</v>
       </c>
       <c r="Y4">
-        <v>0.0357441904651891</v>
+        <v>-0.00753328149870694</v>
       </c>
       <c r="Z4">
-        <v>0.5421033650564705</v>
+        <v>0.3496426434935928</v>
       </c>
       <c r="AA4">
-        <v>0.0007030848690256566</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06449469823636031</v>
+        <v>0.1095887835229679</v>
       </c>
       <c r="AC4">
-        <v>-0.06379161336733466</v>
+        <v>-0.1095887835229679</v>
       </c>
       <c r="AD4">
-        <v>120.9</v>
+        <v>432.8</v>
       </c>
       <c r="AE4">
-        <v>0.4970646607367235</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>121.3970646607367</v>
+        <v>432.8</v>
       </c>
       <c r="AG4">
-        <v>53.09706466073673</v>
+        <v>101.3</v>
       </c>
       <c r="AH4">
-        <v>0.3768959049304088</v>
+        <v>0.5269052836620404</v>
       </c>
       <c r="AI4">
-        <v>0.2875364961579904</v>
+        <v>0.4762323943661972</v>
       </c>
       <c r="AJ4">
-        <v>0.2092107122346519</v>
+        <v>0.2067768932435191</v>
       </c>
       <c r="AK4">
-        <v>0.1500353350249972</v>
+        <v>0.1754720249437035</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>333.9779005524862</v>
-      </c>
-      <c r="AP4">
-        <v>146.6769742009302</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Namibia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Capricorn Group Limited (NMSE:CGP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.06909999999999999</v>
-      </c>
-      <c r="E5">
-        <v>-0.00734</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>61.1</v>
-      </c>
-      <c r="L5">
-        <v>0.2655367231638418</v>
-      </c>
-      <c r="M5">
-        <v>15.51</v>
-      </c>
-      <c r="N5">
-        <v>0.03758177853162104</v>
-      </c>
-      <c r="O5">
-        <v>0.2538461538461538</v>
-      </c>
-      <c r="P5">
-        <v>14.4</v>
-      </c>
-      <c r="Q5">
-        <v>0.03489217349164042</v>
-      </c>
-      <c r="R5">
-        <v>0.2356792144026187</v>
-      </c>
-      <c r="S5">
-        <v>1.109999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.07156673114119919</v>
-      </c>
-      <c r="U5">
-        <v>527.9</v>
-      </c>
-      <c r="V5">
-        <v>1.279137387933123</v>
-      </c>
-      <c r="W5">
-        <v>0.1679032701291564</v>
-      </c>
-      <c r="X5">
-        <v>0.1000140223308689</v>
-      </c>
-      <c r="Y5">
-        <v>0.06788924779828751</v>
-      </c>
-      <c r="Z5">
-        <v>0.5950349107835531</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06690926261152239</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06690926261152239</v>
-      </c>
-      <c r="AD5">
-        <v>546.6</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>546.6</v>
-      </c>
-      <c r="AG5">
-        <v>18.70000000000005</v>
-      </c>
-      <c r="AH5">
-        <v>0.5697904722193267</v>
-      </c>
-      <c r="AI5">
-        <v>0.5233626962849482</v>
-      </c>
-      <c r="AJ5">
-        <v>0.04334724153917488</v>
-      </c>
-      <c r="AK5">
-        <v>0.03620522749273968</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/namibia/namibia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/namibia/namibia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07049999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="E2">
-        <v>0.0284</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.000771840357156038</v>
+        <v>0.0004484865859689095</v>
       </c>
       <c r="J2">
-        <v>0.0005618752516703573</v>
+        <v>0.0003208405654823233</v>
       </c>
       <c r="K2">
-        <v>89.3</v>
+        <v>195.3</v>
       </c>
       <c r="L2">
-        <v>0.247780244173141</v>
+        <v>0.3080441640378548</v>
       </c>
       <c r="M2">
-        <v>33.08000000000001</v>
+        <v>118.83</v>
       </c>
       <c r="N2">
-        <v>0.06311772562488076</v>
+        <v>0.08384251746278135</v>
       </c>
       <c r="O2">
-        <v>0.3704367301231803</v>
+        <v>0.6084485407066053</v>
       </c>
       <c r="P2">
-        <v>31.48</v>
+        <v>114.5</v>
       </c>
       <c r="Q2">
-        <v>0.0600648731158176</v>
+        <v>0.08078741268609328</v>
       </c>
       <c r="R2">
-        <v>0.3525195968645017</v>
+        <v>0.5862775217613928</v>
       </c>
       <c r="S2">
-        <v>1.600000000000001</v>
+        <v>4.330000000000002</v>
       </c>
       <c r="T2">
-        <v>0.04836759371221285</v>
+        <v>0.03643860977867543</v>
       </c>
       <c r="U2">
-        <v>416.1</v>
+        <v>546.9</v>
       </c>
       <c r="V2">
-        <v>0.793932455638237</v>
+        <v>0.3858745502010866</v>
       </c>
       <c r="W2">
-        <v>0.1112936132178734</v>
+        <v>0.163109413614918</v>
       </c>
       <c r="X2">
-        <v>0.1457492804834416</v>
+        <v>0.1013874627829808</v>
       </c>
       <c r="Y2">
-        <v>-0.0344556672655682</v>
+        <v>0.06172195083193723</v>
       </c>
       <c r="Z2">
-        <v>0.3646503116408398</v>
+        <v>0.3883546771974226</v>
       </c>
       <c r="AA2">
-        <v>0.0002868511851250123</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1075501914334558</v>
+        <v>0.08927504076651591</v>
       </c>
       <c r="AC2">
-        <v>-0.1072633402483308</v>
+        <v>-0.08927504076651591</v>
       </c>
       <c r="AD2">
-        <v>585.3</v>
+        <v>945.4</v>
       </c>
       <c r="AE2">
-        <v>0.7241436764048195</v>
+        <v>0.6682975224785567</v>
       </c>
       <c r="AF2">
-        <v>586.0241436764048</v>
+        <v>946.0682975224786</v>
       </c>
       <c r="AG2">
-        <v>169.9241436764048</v>
+        <v>399.1682975224786</v>
       </c>
       <c r="AH2">
-        <v>0.5278906390916471</v>
+        <v>0.4003050639691846</v>
       </c>
       <c r="AI2">
-        <v>0.4373562088884423</v>
+        <v>0.4744412709925317</v>
       </c>
       <c r="AJ2">
-        <v>0.2448389515331235</v>
+        <v>0.2197496637111218</v>
       </c>
       <c r="AK2">
-        <v>0.1839355951449624</v>
+        <v>0.2758271433984881</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1383.687943262411</v>
+        <v>2261.722488038277</v>
       </c>
       <c r="AP2">
-        <v>401.7119235848813</v>
+        <v>954.9480801973173</v>
       </c>
     </row>
     <row r="3">
@@ -715,6 +715,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.0764</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -722,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.00201136127779491</v>
+        <v>0.001900671761392304</v>
       </c>
       <c r="J3">
-        <v>0.001464845684885493</v>
+        <v>0.001360051349833491</v>
       </c>
       <c r="K3">
-        <v>25.4</v>
+        <v>39.9</v>
       </c>
       <c r="L3">
-        <v>0.1836587129428778</v>
+        <v>0.2667112299465241</v>
       </c>
       <c r="M3">
-        <v>9.880000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="N3">
-        <v>0.07291512915129152</v>
+        <v>0.07580778790389395</v>
       </c>
       <c r="O3">
-        <v>0.388976377952756</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="P3">
-        <v>9.880000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="Q3">
-        <v>0.07291512915129152</v>
+        <v>0.07580778790389395</v>
       </c>
       <c r="R3">
-        <v>0.388976377952756</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>84.59999999999999</v>
+        <v>178.2</v>
       </c>
       <c r="V3">
-        <v>0.6243542435424354</v>
+        <v>0.7381938690969345</v>
       </c>
       <c r="W3">
-        <v>0.08472314876584389</v>
+        <v>0.144043321299639</v>
       </c>
       <c r="X3">
-        <v>0.1461012017982734</v>
+        <v>0.1010227494822056</v>
       </c>
       <c r="Y3">
-        <v>-0.06137805303242946</v>
+        <v>0.04302057181743334</v>
       </c>
       <c r="Z3">
-        <v>0.3916469674379871</v>
+        <v>0.432910081950642</v>
       </c>
       <c r="AA3">
-        <v>0.0005737023702500247</v>
+        <v>0.0005887799413134978</v>
       </c>
       <c r="AB3">
-        <v>0.1055115993439438</v>
+        <v>0.08850997796670038</v>
       </c>
       <c r="AC3">
-        <v>-0.1049378969736938</v>
+        <v>-0.08792119802538688</v>
       </c>
       <c r="AD3">
-        <v>152.5</v>
+        <v>146.1</v>
       </c>
       <c r="AE3">
-        <v>0.7241436764048195</v>
+        <v>0.6682975224785567</v>
       </c>
       <c r="AF3">
-        <v>153.2241436764048</v>
+        <v>146.7682975224785</v>
       </c>
       <c r="AG3">
-        <v>68.62414367640483</v>
+        <v>-31.43170247752144</v>
       </c>
       <c r="AH3">
-        <v>0.530693906388843</v>
+        <v>0.3781048026313362</v>
       </c>
       <c r="AI3">
-        <v>0.3554060841264611</v>
+        <v>0.3601072468458709</v>
       </c>
       <c r="AJ3">
-        <v>0.3361882746471859</v>
+        <v>-0.1496973726433938</v>
       </c>
       <c r="AK3">
-        <v>0.1980356778270787</v>
+        <v>-0.1370359496801909</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>360.5200945626478</v>
+        <v>349.5215311004785</v>
       </c>
       <c r="AP3">
-        <v>162.2320181475291</v>
+        <v>-75.19546047253934</v>
       </c>
     </row>
     <row r="4">
@@ -829,117 +835,239 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>FirstRand Namibia Limited (NMSE:FNB)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0582</v>
+      </c>
+      <c r="E4">
+        <v>0.0842</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>82.8</v>
+      </c>
+      <c r="L4">
+        <v>0.3281807372175981</v>
+      </c>
+      <c r="M4">
+        <v>74.5</v>
+      </c>
+      <c r="N4">
+        <v>0.1046495294282905</v>
+      </c>
+      <c r="O4">
+        <v>0.8997584541062802</v>
+      </c>
+      <c r="P4">
+        <v>74.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.1046495294282905</v>
+      </c>
+      <c r="R4">
+        <v>0.8997584541062802</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>67.7</v>
+      </c>
+      <c r="V4">
+        <v>0.09509762607107741</v>
+      </c>
+      <c r="W4">
+        <v>0.2175512348922753</v>
+      </c>
+      <c r="X4">
+        <v>0.1013874627829808</v>
+      </c>
+      <c r="Y4">
+        <v>0.1161637721092946</v>
+      </c>
+      <c r="Z4">
+        <v>0.3387031816351188</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.08927504076651591</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08927504076651591</v>
+      </c>
+      <c r="AD4">
+        <v>441.5</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>441.5</v>
+      </c>
+      <c r="AG4">
+        <v>373.8</v>
+      </c>
+      <c r="AH4">
+        <v>0.3827813421189526</v>
+      </c>
+      <c r="AI4">
+        <v>0.5812269615587151</v>
+      </c>
+      <c r="AJ4">
+        <v>0.344294003868472</v>
+      </c>
+      <c r="AK4">
+        <v>0.540251481427952</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Capricorn Group Limited (NMSE:CGP)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.07049999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.0284</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>63.9</v>
-      </c>
-      <c r="L4">
-        <v>0.2877082395317425</v>
-      </c>
-      <c r="M4">
-        <v>23.2</v>
-      </c>
-      <c r="N4">
-        <v>0.05970149253731344</v>
-      </c>
-      <c r="O4">
-        <v>0.3630672926447575</v>
-      </c>
-      <c r="P4">
-        <v>21.6</v>
-      </c>
-      <c r="Q4">
-        <v>0.05558414822439527</v>
-      </c>
-      <c r="R4">
-        <v>0.3380281690140846</v>
-      </c>
-      <c r="S4">
-        <v>1.600000000000001</v>
-      </c>
-      <c r="T4">
-        <v>0.06896551724137936</v>
-      </c>
-      <c r="U4">
-        <v>331.5</v>
-      </c>
-      <c r="V4">
-        <v>0.8530622748327329</v>
-      </c>
-      <c r="W4">
-        <v>0.1378640776699029</v>
-      </c>
-      <c r="X4">
-        <v>0.1453973591686099</v>
-      </c>
-      <c r="Y4">
-        <v>-0.00753328149870694</v>
-      </c>
-      <c r="Z4">
-        <v>0.3496426434935928</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.1095887835229679</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1095887835229679</v>
-      </c>
-      <c r="AD4">
-        <v>432.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>432.8</v>
-      </c>
-      <c r="AG4">
-        <v>101.3</v>
-      </c>
-      <c r="AH4">
-        <v>0.5269052836620404</v>
-      </c>
-      <c r="AI4">
-        <v>0.4762323943661972</v>
-      </c>
-      <c r="AJ4">
-        <v>0.2067768932435191</v>
-      </c>
-      <c r="AK4">
-        <v>0.1754720249437035</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.0834</v>
+      </c>
+      <c r="E5">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L5">
+        <v>0.3127962085308057</v>
+      </c>
+      <c r="M5">
+        <v>26.03</v>
+      </c>
+      <c r="N5">
+        <v>0.05609913793103449</v>
+      </c>
+      <c r="O5">
+        <v>0.3585399449035813</v>
+      </c>
+      <c r="P5">
+        <v>21.7</v>
+      </c>
+      <c r="Q5">
+        <v>0.04676724137931034</v>
+      </c>
+      <c r="R5">
+        <v>0.2988980716253444</v>
+      </c>
+      <c r="S5">
+        <v>4.330000000000002</v>
+      </c>
+      <c r="T5">
+        <v>0.1663465232424127</v>
+      </c>
+      <c r="U5">
+        <v>301</v>
+      </c>
+      <c r="V5">
+        <v>0.6487068965517241</v>
+      </c>
+      <c r="W5">
+        <v>0.163109413614918</v>
+      </c>
+      <c r="X5">
+        <v>0.1059061720320722</v>
+      </c>
+      <c r="Y5">
+        <v>0.05720324158284582</v>
+      </c>
+      <c r="Z5">
+        <v>0.428181382134819</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.09016179763721094</v>
+      </c>
+      <c r="AC5">
+        <v>-0.09016179763721094</v>
+      </c>
+      <c r="AD5">
+        <v>357.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>357.8</v>
+      </c>
+      <c r="AG5">
+        <v>56.80000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.4353857386225359</v>
+      </c>
+      <c r="AI5">
+        <v>0.4327004474543475</v>
+      </c>
+      <c r="AJ5">
+        <v>0.109062980030722</v>
+      </c>
+      <c r="AK5">
+        <v>0.1080053242061228</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
